--- a/public/sample/입금내역_2026상반기.xlsx
+++ b/public/sample/입금내역_2026상반기.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>입금내역 조회</t>
+          <t>입금내역</t>
         </is>
       </c>
     </row>
@@ -25,133 +25,527 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>보임정밀(주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>거래처</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>세아정밀(주)</t>
-        </is>
-      </c>
-    </row>
+          <t>한빛정밀(주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>조회기간</t>
+          <t>입금일자</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01 ~ 2026-08-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t>보내는분</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>적요</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>입금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>미래모터스(주)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,000,000</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>입금일자</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>입금내역</t>
+          <t>대성테크(주)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>전자결제 입금</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>입금액</t>
+          <t>8,300,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6월 납품 대금</t>
+          <t>한울전자(주)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>전자결제 입금</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8,600,000</t>
+          <t>10,600,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7월 납품 대금</t>
+          <t>동방정공(주)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>전자결제 입금</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10,200,000</t>
+          <t>10,900,000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8월 납품 대금</t>
+          <t>새봄테크(주)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>전자결제 입금</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12,900,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>13,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>한울부품</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13,500,000</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>합계금액</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>미래모터스(주)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31,700,000</t>
+          <t>15,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>대성테크(주)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>한울전자(주)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7,900,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>동방정공(주)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>새봄테크(주)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>한울부품</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>12,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>미래모터스(주)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15,100,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>대성테크(주)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>15,400,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>한울전자(주)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7,200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>동방정공(주)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>새봄테크(주)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>한울부품</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>12,100,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>미래모터스(주)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>12,400,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>대성테크(주)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>14,700,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>한울전자(주)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>15,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>동방정공(주)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>243,300,000</t>
         </is>
       </c>
     </row>

--- a/public/sample/입금내역_2026상반기.xlsx
+++ b/public/sample/입금내역_2026상반기.xlsx
@@ -121,7 +121,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -148,7 +148,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>새봄테크(주)</t>
+          <t>미래모터스(주)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -170,7 +170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한울부품</t>
+          <t>대성테크(주)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -187,12 +187,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>미래모터스(주)</t>
+          <t>한울전자(주)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -209,12 +209,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>대성테크(주)</t>
+          <t>동방정공(주)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한울전자(주)</t>
+          <t>미래모터스(주)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -253,12 +253,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>동방정공(주)</t>
+          <t>대성테크(주)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -275,12 +275,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>새봄테크(주)</t>
+          <t>한울전자(주)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -297,12 +297,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한울부품</t>
+          <t>동방정공(주)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -319,7 +319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -341,7 +341,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -363,7 +363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -407,12 +407,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>새봄테크(주)</t>
+          <t>미래모터스(주)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -429,12 +429,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한울부품</t>
+          <t>대성테크(주)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>미래모터스(주)</t>
+          <t>한울전자(주)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -473,12 +473,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>대성테크(주)</t>
+          <t>동방정공(주)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -492,60 +492,16 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>한울전자(주)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>전자결제 입금</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>15,000,000</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>동방정공(주)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>전자결제 입금</t>
+          <t>합계</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6,800,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>243,300,000</t>
+          <t>221,500,000</t>
         </is>
       </c>
     </row>

--- a/public/sample/입금내역_2026상반기.xlsx
+++ b/public/sample/입금내역_2026상반기.xlsx
@@ -121,7 +121,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -148,7 +148,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>미래모터스(주)</t>
+          <t>새봄테크(주)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -170,7 +170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대성테크(주)</t>
+          <t>한울부품</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -187,12 +187,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한울전자(주)</t>
+          <t>미래모터스(주)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -209,12 +209,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동방정공(주)</t>
+          <t>대성테크(주)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>미래모터스(주)</t>
+          <t>한울전자(주)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -253,12 +253,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>대성테크(주)</t>
+          <t>동방정공(주)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -275,12 +275,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한울전자(주)</t>
+          <t>새봄테크(주)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -297,12 +297,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>동방정공(주)</t>
+          <t>한울부품</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -319,7 +319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -341,7 +341,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -363,7 +363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -385,7 +385,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -407,12 +407,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>미래모터스(주)</t>
+          <t>새봄테크(주)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -429,12 +429,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>대성테크(주)</t>
+          <t>한울부품</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -451,12 +451,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한울전자(주)</t>
+          <t>미래모터스(주)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -473,12 +473,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>동방정공(주)</t>
+          <t>대성테크(주)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -492,16 +492,60 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>한울전자(주)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>15,000,000</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>동방정공(주)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>전자결제 입금</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>221,500,000</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>243,300,000</t>
         </is>
       </c>
     </row>
